--- a/reports/pdf_rolling5_20260629.xlsx
+++ b/reports/pdf_rolling5_20260629.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>바디텍메드  (편출)</t>
         </is>
       </c>
       <c r="F13" s="14" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>199→174</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>바디텍메드  (편출)</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="F15" s="14" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>199→174</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       <c r="C21" s="15" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="F21" s="14" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>88→70</t>
+          <t>138→120</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       <c r="C22" s="15" t="n"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="F22" s="14" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>151→133</t>
+          <t>88→70</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       <c r="C24" s="15" t="n"/>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="F24" s="14" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>138→120</t>
+          <t>151→133</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       <c r="C32" s="15" t="n"/>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="F32" s="14" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>182→179</t>
+          <t>216→213</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       <c r="C34" s="15" t="n"/>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="F34" s="14" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>216→213</t>
+          <t>182→179</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>HK이노엔  (신규)</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>29→40</t>
+          <t>0→11</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>HK이노엔  (신규)</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>0→11</t>
+          <t>29→40</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -2298,7 +2298,7 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>64→68</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="E80" s="15" t="n"/>
@@ -2316,7 +2316,7 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>64→68</t>
         </is>
       </c>
       <c r="E81" s="15" t="n"/>
